--- a/sample_sales_data/Sales_March_2026.xlsx
+++ b/sample_sales_data/Sales_March_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="137">
   <si>
     <t>Item ID</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Unit Price ($)</t>
-  </si>
-  <si>
-    <t>Total Sales ($)</t>
   </si>
   <si>
     <t>ITM-1000</t>
@@ -1664,22 +1661,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E4" s="3">
         <v>150</v>
@@ -1687,23 +1682,20 @@
       <c r="F4" s="4">
         <v>80.11</v>
       </c>
-      <c r="G4" s="4">
-        <f t="shared" ref="G4:G63" si="0">E4*F4</f>
-        <v>12016.5</v>
-      </c>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="3">
         <v>176</v>
@@ -1711,23 +1703,20 @@
       <c r="F5" s="4">
         <v>13.42</v>
       </c>
-      <c r="G5" s="4">
-        <f t="shared" si="0"/>
-        <v>2361.92</v>
-      </c>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E6" s="3">
         <v>349</v>
@@ -1735,23 +1724,20 @@
       <c r="F6" s="4">
         <v>16.67</v>
       </c>
-      <c r="G6" s="4">
-        <f t="shared" si="0"/>
-        <v>5817.83</v>
-      </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="3">
         <v>80</v>
@@ -1759,23 +1745,20 @@
       <c r="F7" s="4">
         <v>9.51</v>
       </c>
-      <c r="G7" s="4">
-        <f t="shared" si="0"/>
-        <v>760.8</v>
-      </c>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3">
         <v>248</v>
@@ -1783,23 +1766,20 @@
       <c r="F8" s="4">
         <v>60.66</v>
       </c>
-      <c r="G8" s="4">
-        <f t="shared" si="0"/>
-        <v>15043.68</v>
-      </c>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E9" s="3">
         <v>238</v>
@@ -1807,23 +1787,20 @@
       <c r="F9" s="4">
         <v>22.79</v>
       </c>
-      <c r="G9" s="4">
-        <f t="shared" si="0"/>
-        <v>5424.02</v>
-      </c>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" s="3">
         <v>104</v>
@@ -1831,23 +1808,20 @@
       <c r="F10" s="4">
         <v>35.75</v>
       </c>
-      <c r="G10" s="4">
-        <f t="shared" si="0"/>
-        <v>3718</v>
-      </c>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E11" s="3">
         <v>258</v>
@@ -1855,23 +1829,20 @@
       <c r="F11" s="4">
         <v>148.48</v>
       </c>
-      <c r="G11" s="4">
-        <f t="shared" si="0"/>
-        <v>38307.84</v>
-      </c>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="3">
         <v>340</v>
@@ -1879,23 +1850,20 @@
       <c r="F12" s="4">
         <v>91.68</v>
       </c>
-      <c r="G12" s="4">
-        <f t="shared" si="0"/>
-        <v>31171.2</v>
-      </c>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3">
         <v>403</v>
@@ -1903,23 +1871,20 @@
       <c r="F13" s="4">
         <v>79.39</v>
       </c>
-      <c r="G13" s="4">
-        <f t="shared" si="0"/>
-        <v>31994.17</v>
-      </c>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" s="3">
         <v>416</v>
@@ -1927,23 +1892,20 @@
       <c r="F14" s="4">
         <v>198.69</v>
       </c>
-      <c r="G14" s="4">
-        <f t="shared" si="0"/>
-        <v>82655.04</v>
-      </c>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="3">
         <v>242</v>
@@ -1951,23 +1913,20 @@
       <c r="F15" s="4">
         <v>15.27</v>
       </c>
-      <c r="G15" s="4">
-        <f t="shared" si="0"/>
-        <v>3695.34</v>
-      </c>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E16" s="3">
         <v>474</v>
@@ -1975,23 +1934,20 @@
       <c r="F16" s="4">
         <v>20.69</v>
       </c>
-      <c r="G16" s="4">
-        <f t="shared" si="0"/>
-        <v>9807.06</v>
-      </c>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3">
         <v>73</v>
@@ -1999,23 +1955,20 @@
       <c r="F17" s="4">
         <v>46.35</v>
       </c>
-      <c r="G17" s="4">
-        <f t="shared" si="0"/>
-        <v>3383.55</v>
-      </c>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3">
         <v>291</v>
@@ -2023,23 +1976,20 @@
       <c r="F18" s="4">
         <v>40.37</v>
       </c>
-      <c r="G18" s="4">
-        <f t="shared" si="0"/>
-        <v>11747.67</v>
-      </c>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="3">
         <v>318</v>
@@ -2047,23 +1997,20 @@
       <c r="F19" s="4">
         <v>25.78</v>
       </c>
-      <c r="G19" s="4">
-        <f t="shared" si="0"/>
-        <v>8198.04</v>
-      </c>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="3">
         <v>223</v>
@@ -2071,23 +2018,20 @@
       <c r="F20" s="4">
         <v>15.49</v>
       </c>
-      <c r="G20" s="4">
-        <f t="shared" si="0"/>
-        <v>3454.27</v>
-      </c>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="3">
         <v>233</v>
@@ -2095,23 +2039,20 @@
       <c r="F21" s="4">
         <v>23.9</v>
       </c>
-      <c r="G21" s="4">
-        <f t="shared" si="0"/>
-        <v>5568.7</v>
-      </c>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" s="3">
         <v>235</v>
@@ -2119,23 +2060,20 @@
       <c r="F22" s="4">
         <v>6.33</v>
       </c>
-      <c r="G22" s="4">
-        <f t="shared" si="0"/>
-        <v>1487.55</v>
-      </c>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" s="3">
         <v>435</v>
@@ -2143,23 +2081,20 @@
       <c r="F23" s="4">
         <v>22.29</v>
       </c>
-      <c r="G23" s="4">
-        <f t="shared" si="0"/>
-        <v>9696.15</v>
-      </c>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="3">
         <v>253</v>
@@ -2167,23 +2102,20 @@
       <c r="F24" s="4">
         <v>50.62</v>
       </c>
-      <c r="G24" s="4">
-        <f t="shared" si="0"/>
-        <v>12806.86</v>
-      </c>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E25" s="3">
         <v>230</v>
@@ -2191,23 +2123,20 @@
       <c r="F25" s="4">
         <v>38.3</v>
       </c>
-      <c r="G25" s="4">
-        <f t="shared" si="0"/>
-        <v>8809</v>
-      </c>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="3">
         <v>125</v>
@@ -2215,23 +2144,20 @@
       <c r="F26" s="4">
         <v>32.24</v>
       </c>
-      <c r="G26" s="4">
-        <f t="shared" si="0"/>
-        <v>4030</v>
-      </c>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="3">
         <v>462</v>
@@ -2239,23 +2165,20 @@
       <c r="F27" s="4">
         <v>18.06</v>
       </c>
-      <c r="G27" s="4">
-        <f t="shared" si="0"/>
-        <v>8343.72</v>
-      </c>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" s="3">
         <v>82</v>
@@ -2263,23 +2186,20 @@
       <c r="F28" s="4">
         <v>24.32</v>
       </c>
-      <c r="G28" s="4">
-        <f t="shared" si="0"/>
-        <v>1994.24</v>
-      </c>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" s="3">
         <v>366</v>
@@ -2287,23 +2207,20 @@
       <c r="F29" s="4">
         <v>27.19</v>
       </c>
-      <c r="G29" s="4">
-        <f t="shared" si="0"/>
-        <v>9951.54</v>
-      </c>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30" s="3">
         <v>213</v>
@@ -2311,23 +2228,20 @@
       <c r="F30" s="4">
         <v>24.57</v>
       </c>
-      <c r="G30" s="4">
-        <f t="shared" si="0"/>
-        <v>5233.41</v>
-      </c>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" s="3">
         <v>217</v>
@@ -2335,23 +2249,20 @@
       <c r="F31" s="4">
         <v>19.11</v>
       </c>
-      <c r="G31" s="4">
-        <f t="shared" si="0"/>
-        <v>4146.87</v>
-      </c>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" s="3">
         <v>204</v>
@@ -2359,23 +2270,20 @@
       <c r="F32" s="4">
         <v>67.62</v>
       </c>
-      <c r="G32" s="4">
-        <f t="shared" si="0"/>
-        <v>13794.48</v>
-      </c>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" s="3">
         <v>489</v>
@@ -2383,23 +2291,20 @@
       <c r="F33" s="4">
         <v>35.67</v>
       </c>
-      <c r="G33" s="4">
-        <f t="shared" si="0"/>
-        <v>17442.63</v>
-      </c>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="3">
         <v>199</v>
@@ -2407,23 +2312,20 @@
       <c r="F34" s="4">
         <v>3.98</v>
       </c>
-      <c r="G34" s="4">
-        <f t="shared" si="0"/>
-        <v>792.02</v>
-      </c>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" s="3">
         <v>157</v>
@@ -2431,23 +2333,20 @@
       <c r="F35" s="4">
         <v>3.07</v>
       </c>
-      <c r="G35" s="4">
-        <f t="shared" si="0"/>
-        <v>481.99</v>
-      </c>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E36" s="3">
         <v>280</v>
@@ -2455,23 +2354,20 @@
       <c r="F36" s="4">
         <v>56.35</v>
       </c>
-      <c r="G36" s="4">
-        <f t="shared" si="0"/>
-        <v>15778</v>
-      </c>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" s="3">
         <v>414</v>
@@ -2479,23 +2375,20 @@
       <c r="F37" s="4">
         <v>9.08</v>
       </c>
-      <c r="G37" s="4">
-        <f t="shared" si="0"/>
-        <v>3759.12</v>
-      </c>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" s="3">
         <v>254</v>
@@ -2503,23 +2396,20 @@
       <c r="F38" s="4">
         <v>24.29</v>
       </c>
-      <c r="G38" s="4">
-        <f t="shared" si="0"/>
-        <v>6169.66</v>
-      </c>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E39" s="3">
         <v>253</v>
@@ -2527,23 +2417,20 @@
       <c r="F39" s="4">
         <v>26.67</v>
       </c>
-      <c r="G39" s="4">
-        <f t="shared" si="0"/>
-        <v>6747.51</v>
-      </c>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E40" s="3">
         <v>347</v>
@@ -2551,23 +2438,20 @@
       <c r="F40" s="4">
         <v>19.33</v>
       </c>
-      <c r="G40" s="4">
-        <f t="shared" si="0"/>
-        <v>6707.51</v>
-      </c>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E41" s="3">
         <v>375</v>
@@ -2575,23 +2459,20 @@
       <c r="F41" s="4">
         <v>115.97</v>
       </c>
-      <c r="G41" s="4">
-        <f t="shared" si="0"/>
-        <v>43488.75</v>
-      </c>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E42" s="3">
         <v>475</v>
@@ -2599,23 +2480,20 @@
       <c r="F42" s="4">
         <v>4.8</v>
       </c>
-      <c r="G42" s="4">
-        <f t="shared" si="0"/>
-        <v>2280</v>
-      </c>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" s="3">
         <v>278</v>
@@ -2623,23 +2501,20 @@
       <c r="F43" s="4">
         <v>28.57</v>
       </c>
-      <c r="G43" s="4">
-        <f t="shared" si="0"/>
-        <v>7942.46</v>
-      </c>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E44" s="3">
         <v>308</v>
@@ -2647,23 +2522,20 @@
       <c r="F44" s="4">
         <v>7.04</v>
       </c>
-      <c r="G44" s="4">
-        <f t="shared" si="0"/>
-        <v>2168.32</v>
-      </c>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" s="3">
         <v>47</v>
@@ -2671,23 +2543,20 @@
       <c r="F45" s="4">
         <v>131.85</v>
       </c>
-      <c r="G45" s="4">
-        <f t="shared" si="0"/>
-        <v>6196.95</v>
-      </c>
+      <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="C46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E46" s="3">
         <v>448</v>
@@ -2695,23 +2564,20 @@
       <c r="F46" s="4">
         <v>29.88</v>
       </c>
-      <c r="G46" s="4">
-        <f t="shared" si="0"/>
-        <v>13386.24</v>
-      </c>
+      <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" s="3">
         <v>138</v>
@@ -2719,23 +2585,20 @@
       <c r="F47" s="4">
         <v>12.83</v>
       </c>
-      <c r="G47" s="4">
-        <f t="shared" si="0"/>
-        <v>1770.54</v>
-      </c>
+      <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" s="3">
         <v>237</v>
@@ -2743,23 +2606,20 @@
       <c r="F48" s="4">
         <v>11.78</v>
       </c>
-      <c r="G48" s="4">
-        <f t="shared" si="0"/>
-        <v>2791.86</v>
-      </c>
+      <c r="G48" s="4"/>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E49" s="3">
         <v>147</v>
@@ -2767,23 +2627,20 @@
       <c r="F49" s="4">
         <v>71.75</v>
       </c>
-      <c r="G49" s="4">
-        <f t="shared" si="0"/>
-        <v>10547.25</v>
-      </c>
+      <c r="G49" s="4"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E50" s="3">
         <v>134</v>
@@ -2791,23 +2648,20 @@
       <c r="F50" s="4">
         <v>62</v>
       </c>
-      <c r="G50" s="4">
-        <f t="shared" si="0"/>
-        <v>8308</v>
-      </c>
+      <c r="G50" s="4"/>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E51" s="3">
         <v>14</v>
@@ -2815,23 +2669,20 @@
       <c r="F51" s="4">
         <v>10.24</v>
       </c>
-      <c r="G51" s="4">
-        <f t="shared" si="0"/>
-        <v>143.36</v>
-      </c>
+      <c r="G51" s="4"/>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52" s="3">
         <v>492</v>
@@ -2839,23 +2690,20 @@
       <c r="F52" s="4">
         <v>147.74</v>
       </c>
-      <c r="G52" s="4">
-        <f t="shared" si="0"/>
-        <v>72688.08</v>
-      </c>
+      <c r="G52" s="4"/>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E53" s="3">
         <v>404</v>
@@ -2863,23 +2711,20 @@
       <c r="F53" s="4">
         <v>104.56</v>
       </c>
-      <c r="G53" s="4">
-        <f t="shared" si="0"/>
-        <v>42242.24</v>
-      </c>
+      <c r="G53" s="4"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54" s="3">
         <v>391</v>
@@ -2887,23 +2732,20 @@
       <c r="F54" s="4">
         <v>19.05</v>
       </c>
-      <c r="G54" s="4">
-        <f t="shared" si="0"/>
-        <v>7448.55</v>
-      </c>
+      <c r="G54" s="4"/>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E55" s="3">
         <v>107</v>
@@ -2911,23 +2753,20 @@
       <c r="F55" s="4">
         <v>8.26</v>
       </c>
-      <c r="G55" s="4">
-        <f t="shared" si="0"/>
-        <v>883.82</v>
-      </c>
+      <c r="G55" s="4"/>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56" s="3">
         <v>83</v>
@@ -2935,23 +2774,20 @@
       <c r="F56" s="4">
         <v>12.65</v>
       </c>
-      <c r="G56" s="4">
-        <f t="shared" si="0"/>
-        <v>1049.95</v>
-      </c>
+      <c r="G56" s="4"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E57" s="3">
         <v>347</v>
@@ -2959,23 +2795,20 @@
       <c r="F57" s="4">
         <v>28.83</v>
       </c>
-      <c r="G57" s="4">
-        <f t="shared" si="0"/>
-        <v>10004.01</v>
-      </c>
+      <c r="G57" s="4"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E58" s="3">
         <v>243</v>
@@ -2983,23 +2816,20 @@
       <c r="F58" s="4">
         <v>50.99</v>
       </c>
-      <c r="G58" s="4">
-        <f t="shared" si="0"/>
-        <v>12390.57</v>
-      </c>
+      <c r="G58" s="4"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E59" s="3">
         <v>90</v>
@@ -3007,23 +2837,20 @@
       <c r="F59" s="4">
         <v>353.7</v>
       </c>
-      <c r="G59" s="4">
-        <f t="shared" si="0"/>
-        <v>31833</v>
-      </c>
+      <c r="G59" s="4"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E60" s="3">
         <v>403</v>
@@ -3031,23 +2858,20 @@
       <c r="F60" s="4">
         <v>46.43</v>
       </c>
-      <c r="G60" s="4">
-        <f t="shared" si="0"/>
-        <v>18711.29</v>
-      </c>
+      <c r="G60" s="4"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="C61" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E61" s="3">
         <v>60</v>
@@ -3055,23 +2879,20 @@
       <c r="F61" s="4">
         <v>6.04</v>
       </c>
-      <c r="G61" s="4">
-        <f t="shared" si="0"/>
-        <v>362.4</v>
-      </c>
+      <c r="G61" s="4"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C62" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E62" s="3">
         <v>299</v>
@@ -3079,23 +2900,20 @@
       <c r="F62" s="4">
         <v>91.59</v>
       </c>
-      <c r="G62" s="4">
-        <f t="shared" si="0"/>
-        <v>27385.41</v>
-      </c>
+      <c r="G62" s="4"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C63" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E63" s="3">
         <v>208</v>
@@ -3103,10 +2921,7 @@
       <c r="F63" s="4">
         <v>135.73</v>
       </c>
-      <c r="G63" s="4">
-        <f t="shared" si="0"/>
-        <v>28231.84</v>
-      </c>
+      <c r="G63" s="4"/>
     </row>
     <row r="65" spans="4:7">
       <c r="D65" s="5"/>
